--- a/assets/constructions/examples/ctd_mhr.xlsx
+++ b/assets/constructions/examples/ctd_mhr.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,71 +629,100 @@
           <t>kwy</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MM EA080B05R0.5-3T05 IC08</t>
+          <t>BR-B7.100R010.A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>BRICE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MM EA</t>
+          <t>BR-B7-R</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>PMSH</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
       <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>BRICE_BR10</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>5</v>
       </c>
-      <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ISCAR_MM:T05</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>WORKPIECE</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>IC08</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>AlTiN</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -701,27 +730,29 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="Z2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>3</v>
+      </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2013/Multi_Master_Catalog.pdf</t>
+          <t>02/2019</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -732,114 +763,149 @@
       <c r="AI2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>e8</t>
+        </is>
+      </c>
       <c r="AK2" t="b">
         <v>0</v>
       </c>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Z_BR10</t>
+        </is>
+      </c>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>57482503DL25 WS15PE</t>
+          <t>A316-12SM210-05015P 1030</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>CoroMill® 316..SM2..P</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PS</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
+          <t>PMKS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>12.7</v>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>1.575</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>37.5</v>
+        <v>10.5</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>37.5</v>
+        <v>10.5</v>
       </c>
       <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>INCH_EH:12</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>5</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>DUOLOCK:DL25</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>WORKPIECE</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>WS15PE</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>AlTiN</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>PVD(Ti,Al)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>COROMANT</t>
+        </is>
+      </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>24</v>
+        <v>12.3</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>12.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.035</v>
+      </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2018/Achievements RU</t>
+          <t>11,2</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -850,26 +916,29 @@
       <c r="AI3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>e8</t>
-        </is>
-      </c>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>ZDL25</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MM EC160B12R0.5-8T10 IC908</t>
+          <t>MM EA200B12R1.0-3T12 IC08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -879,21 +948,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MM EC-8/MM EC-10</t>
+          <t>MM EA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMKSH</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>12</v>
@@ -908,11 +977,11 @@
         <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ISCAR_MM:T10</t>
+          <t>ISCAR_MM:T12</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -923,13 +992,13 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>IC908</t>
+          <t>IC08</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -937,11 +1006,11 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>15.3</v>
+        <v>18.45</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>20.5</v>
+        <v>25.5</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
@@ -966,7 +1035,7 @@
         </is>
       </c>
       <c r="AI4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="b">
@@ -975,35 +1044,52 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MM EC160B12R2.0-8T10 IC908</t>
+          <t>XSEME01120050</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MM EC-8/MM EC-10</t>
+          <t>XSEME01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PMKSH</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
       <c r="F5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="G5" t="n">
+        <v>11</v>
+      </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="I5" t="n">
         <v>12</v>
@@ -1018,11 +1104,11 @@
         <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ISCAR_MM:T10</t>
+          <t>METRIC_THREAD:M6</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1031,15 +1117,11 @@
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>IC908</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>Y-Coating</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1047,15 +1129,17 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>12</v>
+      </c>
       <c r="X5" t="n">
         <v>20.5</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
@@ -1067,7 +1151,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2013/Multi_Master_Catalog.pdf</t>
+          <t>YG1 I_SMART_END_MILLS</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1083,13 +1167,36 @@
         <v>0</v>
       </c>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>107.26</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR5" t="n">
+        <v>9860.809999999999</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>PKH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XSEME01100300</t>
+          <t>XSEME68250050</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1099,7 +1206,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>XSEME01</t>
+          <t>XSEME68</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1113,32 +1220,32 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M6</t>
+          <t>METRIC_THREAD:M12</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1159,17 +1266,17 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="W6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>37</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
@@ -1190,7 +1297,7 @@
         </is>
       </c>
       <c r="AI6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="b">
@@ -1198,10 +1305,29 @@
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AN6" t="n">
-        <v>8</v>
+        <v>22</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>375.25</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR6" t="n">
+        <v>34498.12</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>PKH</t>
+        </is>
       </c>
     </row>
   </sheetData>
